--- a/experiments/classical_ml_M5Pro.xlsx
+++ b/experiments/classical_ml_M5Pro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ngod\working\vscode\CS5242\experiments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/david/working/antigravity/CS5242/experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16EB8DE-5D8B-42F8-83D8-13042A0737AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B13C6C1-1F1F-EC41-A5D4-D6A3CE33E103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F4B42735-54A6-4943-A174-BDC00D6EDFCD}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="17520" xr2:uid="{F4B42735-54A6-4943-A174-BDC00D6EDFCD}"/>
   </bookViews>
   <sheets>
     <sheet name="M5Pro" sheetId="1" r:id="rId1"/>
@@ -113,7 +113,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -129,6 +129,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -160,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -177,6 +183,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -513,20 +523,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E1E373F-8B5E-4AA1-B1CE-A13674CA8A61}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.5" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -552,7 +563,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -578,7 +589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -604,7 +615,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -630,7 +641,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -656,7 +667,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -682,7 +693,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
@@ -708,7 +719,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -734,7 +745,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
@@ -760,7 +771,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -786,7 +797,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -812,7 +823,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -838,7 +849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
@@ -864,33 +875,33 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="9">
         <v>0.87009999999999998</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="9">
         <v>0.83199999999999996</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="9">
         <v>99</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="9">
         <v>254.3</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="9">
         <v>224</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H14" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>11</v>
       </c>
@@ -916,33 +927,33 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="9">
         <v>0.90469999999999995</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="9">
         <v>0.871</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="9">
         <v>98.9</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="9">
         <v>12</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="9">
         <v>224</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H16" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>11</v>
       </c>
@@ -968,7 +979,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>12</v>
       </c>
@@ -994,7 +1005,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>12</v>
       </c>
@@ -1020,7 +1031,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>12</v>
       </c>
@@ -1046,7 +1057,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>12</v>
       </c>
@@ -1072,7 +1083,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>13</v>
       </c>
@@ -1098,7 +1109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>13</v>
       </c>
@@ -1124,7 +1135,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>13</v>
       </c>
@@ -1150,7 +1161,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>13</v>
       </c>
@@ -1177,6 +1188,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H25" xr:uid="{4E1E373F-8B5E-4AA1-B1CE-A13674CA8A61}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="224"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/experiments/classical_ml_M5Pro.xlsx
+++ b/experiments/classical_ml_M5Pro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/david/working/antigravity/CS5242/experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B13C6C1-1F1F-EC41-A5D4-D6A3CE33E103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A6EDAE-75CC-894A-8588-DB4DD7BD2E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="17520" xr2:uid="{F4B42735-54A6-4943-A174-BDC00D6EDFCD}"/>
   </bookViews>

--- a/experiments/classical_ml_M5Pro.xlsx
+++ b/experiments/classical_ml_M5Pro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/david/working/antigravity/CS5242/experiments/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ngod\working\antigravity\CS5242\experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A6EDAE-75CC-894A-8588-DB4DD7BD2E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D27E18-AD55-4382-9B37-A059BD186581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="17520" xr2:uid="{F4B42735-54A6-4943-A174-BDC00D6EDFCD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{F4B42735-54A6-4943-A174-BDC00D6EDFCD}"/>
   </bookViews>
   <sheets>
     <sheet name="M5Pro" sheetId="1" r:id="rId1"/>
@@ -523,21 +523,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E1E373F-8B5E-4AA1-B1CE-A13674CA8A61}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.42578125" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -563,76 +562,76 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="9">
         <v>0.98350000000000004</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="9">
         <v>0.93899999999999995</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="9">
         <v>227.1</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="9">
         <v>127.4</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="9">
         <v>224</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="H2" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="9">
+        <v>0.98409999999999997</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0.94840000000000002</v>
+      </c>
+      <c r="E3" s="9">
+        <v>241.9</v>
+      </c>
+      <c r="F3" s="9">
+        <v>3.4</v>
+      </c>
+      <c r="G3" s="9">
+        <v>224</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6">
-        <v>0.44950000000000001</v>
-      </c>
-      <c r="D3" s="6">
-        <v>0.43240000000000001</v>
-      </c>
-      <c r="E3" s="6">
-        <v>76.900000000000006</v>
-      </c>
-      <c r="F3" s="6">
-        <v>537.70000000000005</v>
-      </c>
-      <c r="G3" s="6">
-        <v>32</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="C4" s="5">
-        <v>0.98409999999999997</v>
+        <v>0.95720000000000005</v>
       </c>
       <c r="D4" s="5">
-        <v>0.94840000000000002</v>
+        <v>0.91920000000000002</v>
       </c>
       <c r="E4" s="5">
-        <v>241.9</v>
+        <v>108.8</v>
       </c>
       <c r="F4" s="5">
-        <v>3.4</v>
+        <v>1685.7</v>
       </c>
       <c r="G4" s="5">
         <v>224</v>
@@ -641,50 +640,50 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="6">
-        <v>0.45789999999999997</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0.44219999999999998</v>
-      </c>
-      <c r="E5" s="6">
-        <v>77.599999999999994</v>
-      </c>
-      <c r="F5" s="6">
-        <v>20.8</v>
-      </c>
-      <c r="G5" s="6">
-        <v>32</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C5" s="5">
+        <v>0.96289999999999998</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="E5" s="5">
+        <v>108.3</v>
+      </c>
+      <c r="F5" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="G5" s="5">
+        <v>224</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="5">
-        <v>0.95720000000000005</v>
+        <v>0.96650000000000003</v>
       </c>
       <c r="D6" s="5">
-        <v>0.91920000000000002</v>
+        <v>0.92559999999999998</v>
       </c>
       <c r="E6" s="5">
-        <v>108.8</v>
+        <v>132.1</v>
       </c>
       <c r="F6" s="5">
-        <v>1685.7</v>
+        <v>336.7</v>
       </c>
       <c r="G6" s="5">
         <v>224</v>
@@ -693,102 +692,102 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.9708</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.93440000000000001</v>
+      </c>
+      <c r="E7" s="5">
+        <v>133.1</v>
+      </c>
+      <c r="F7" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="G7" s="5">
+        <v>224</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="6">
-        <v>0.2485</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0.2382</v>
-      </c>
-      <c r="E7" s="6">
-        <v>77.8</v>
-      </c>
-      <c r="F7" s="6">
-        <v>1312.7</v>
-      </c>
-      <c r="G7" s="6">
-        <v>32</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="9">
+        <v>0.87009999999999998</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0.83199999999999996</v>
+      </c>
+      <c r="E8" s="9">
+        <v>99</v>
+      </c>
+      <c r="F8" s="9">
+        <v>254.3</v>
+      </c>
+      <c r="G8" s="9">
+        <v>224</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="5">
-        <v>0.96289999999999998</v>
-      </c>
-      <c r="D8" s="5">
-        <v>0.92500000000000004</v>
-      </c>
-      <c r="E8" s="5">
-        <v>108.3</v>
-      </c>
-      <c r="F8" s="5">
-        <v>3.3</v>
-      </c>
-      <c r="G8" s="5">
+      <c r="C9" s="9">
+        <v>0.90469999999999995</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0.871</v>
+      </c>
+      <c r="E9" s="9">
+        <v>98.9</v>
+      </c>
+      <c r="F9" s="9">
+        <v>12</v>
+      </c>
+      <c r="G9" s="9">
         <v>224</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.26090000000000002</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0.246</v>
-      </c>
-      <c r="E9" s="6">
-        <v>78.400000000000006</v>
-      </c>
-      <c r="F9" s="6">
-        <v>45.5</v>
-      </c>
-      <c r="G9" s="6">
-        <v>32</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="5">
-        <v>0.96650000000000003</v>
+        <v>0.91339999999999999</v>
       </c>
       <c r="D10" s="5">
-        <v>0.92559999999999998</v>
+        <v>0.85680000000000001</v>
       </c>
       <c r="E10" s="5">
-        <v>132.1</v>
+        <v>118.6</v>
       </c>
       <c r="F10" s="5">
-        <v>336.7</v>
+        <v>187.4</v>
       </c>
       <c r="G10" s="5">
         <v>224</v>
@@ -797,50 +796,50 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.93989999999999996</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0.88719999999999999</v>
+      </c>
+      <c r="E11" s="5">
+        <v>118.4</v>
+      </c>
+      <c r="F11" s="5">
+        <v>8.9</v>
+      </c>
+      <c r="G11" s="5">
+        <v>224</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.19689999999999999</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0.19220000000000001</v>
-      </c>
-      <c r="E11" s="6">
-        <v>78.2</v>
-      </c>
-      <c r="F11" s="6">
-        <v>9618.4</v>
-      </c>
-      <c r="G11" s="6">
-        <v>32</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="C12" s="5">
         <v>0.9708</v>
       </c>
       <c r="D12" s="5">
-        <v>0.93440000000000001</v>
+        <v>0.93259999999999998</v>
       </c>
       <c r="E12" s="5">
-        <v>133.1</v>
+        <v>194</v>
       </c>
       <c r="F12" s="5">
-        <v>3.3</v>
+        <v>661.9</v>
       </c>
       <c r="G12" s="5">
         <v>224</v>
@@ -849,76 +848,76 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="6">
-        <v>0.22209999999999999</v>
-      </c>
-      <c r="D13" s="6">
-        <v>0.2084</v>
-      </c>
-      <c r="E13" s="6">
-        <v>77.400000000000006</v>
-      </c>
-      <c r="F13" s="6">
-        <v>223.6</v>
-      </c>
-      <c r="G13" s="6">
+      <c r="C13" s="5">
+        <v>0.97489999999999999</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.94479999999999997</v>
+      </c>
+      <c r="E13" s="5">
+        <v>195.5</v>
+      </c>
+      <c r="F13" s="5">
+        <v>8.9</v>
+      </c>
+      <c r="G13" s="5">
+        <v>224</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.44950000000000001</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0.43240000000000001</v>
+      </c>
+      <c r="E14" s="6">
+        <v>76.900000000000006</v>
+      </c>
+      <c r="F14" s="6">
+        <v>537.70000000000005</v>
+      </c>
+      <c r="G14" s="6">
         <v>32</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="9">
-        <v>0.87009999999999998</v>
-      </c>
-      <c r="D14" s="9">
-        <v>0.83199999999999996</v>
-      </c>
-      <c r="E14" s="9">
-        <v>99</v>
-      </c>
-      <c r="F14" s="9">
-        <v>254.3</v>
-      </c>
-      <c r="G14" s="9">
-        <v>224</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="H14" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>0.34050000000000002</v>
+        <v>0.45789999999999997</v>
       </c>
       <c r="D15" s="6">
-        <v>0.32519999999999999</v>
+        <v>0.44219999999999998</v>
       </c>
       <c r="E15" s="6">
-        <v>76.5</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="F15" s="6">
-        <v>142.5</v>
+        <v>20.8</v>
       </c>
       <c r="G15" s="6">
         <v>32</v>
@@ -927,50 +926,50 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="9">
-        <v>0.90469999999999995</v>
-      </c>
-      <c r="D16" s="9">
-        <v>0.871</v>
-      </c>
-      <c r="E16" s="9">
-        <v>98.9</v>
-      </c>
-      <c r="F16" s="9">
-        <v>12</v>
-      </c>
-      <c r="G16" s="9">
-        <v>224</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.2485</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.2382</v>
+      </c>
+      <c r="E16" s="6">
+        <v>77.8</v>
+      </c>
+      <c r="F16" s="6">
+        <v>1312.7</v>
+      </c>
+      <c r="G16" s="6">
+        <v>32</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>0.34150000000000003</v>
+        <v>0.26090000000000002</v>
       </c>
       <c r="D17" s="6">
-        <v>0.32540000000000002</v>
+        <v>0.246</v>
       </c>
       <c r="E17" s="6">
-        <v>77.7</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="F17" s="6">
-        <v>30.7</v>
+        <v>45.5</v>
       </c>
       <c r="G17" s="6">
         <v>32</v>
@@ -979,50 +978,50 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="5">
-        <v>0.91339999999999999</v>
-      </c>
-      <c r="D18" s="5">
-        <v>0.85680000000000001</v>
-      </c>
-      <c r="E18" s="5">
-        <v>118.6</v>
-      </c>
-      <c r="F18" s="5">
-        <v>187.4</v>
-      </c>
-      <c r="G18" s="5">
-        <v>224</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="C18" s="6">
+        <v>0.19689999999999999</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.19220000000000001</v>
+      </c>
+      <c r="E18" s="6">
+        <v>78.2</v>
+      </c>
+      <c r="F18" s="6">
+        <v>9618.4</v>
+      </c>
+      <c r="G18" s="6">
+        <v>32</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>0.3614</v>
+        <v>0.22209999999999999</v>
       </c>
       <c r="D19" s="6">
-        <v>0.3306</v>
+        <v>0.2084</v>
       </c>
       <c r="E19" s="6">
-        <v>77.3</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="F19" s="6">
-        <v>206</v>
+        <v>223.6</v>
       </c>
       <c r="G19" s="6">
         <v>32</v>
@@ -1031,50 +1030,50 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>0.93989999999999996</v>
-      </c>
-      <c r="D20" s="5">
-        <v>0.88719999999999999</v>
-      </c>
-      <c r="E20" s="5">
-        <v>118.4</v>
-      </c>
-      <c r="F20" s="5">
-        <v>8.9</v>
-      </c>
-      <c r="G20" s="5">
-        <v>224</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.34050000000000002</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0.32519999999999999</v>
+      </c>
+      <c r="E20" s="6">
+        <v>76.5</v>
+      </c>
+      <c r="F20" s="6">
+        <v>142.5</v>
+      </c>
+      <c r="G20" s="6">
+        <v>32</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>0.35139999999999999</v>
+        <v>0.34150000000000003</v>
       </c>
       <c r="D21" s="6">
-        <v>0.3306</v>
+        <v>0.32540000000000002</v>
       </c>
       <c r="E21" s="6">
-        <v>76.900000000000006</v>
+        <v>77.7</v>
       </c>
       <c r="F21" s="6">
-        <v>58.4</v>
+        <v>30.7</v>
       </c>
       <c r="G21" s="6">
         <v>32</v>
@@ -1083,50 +1082,50 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="5">
-        <v>0.9708</v>
-      </c>
-      <c r="D22" s="5">
-        <v>0.93259999999999998</v>
-      </c>
-      <c r="E22" s="5">
-        <v>194</v>
-      </c>
-      <c r="F22" s="5">
-        <v>661.9</v>
-      </c>
-      <c r="G22" s="5">
-        <v>224</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="C22" s="6">
+        <v>0.3614</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0.3306</v>
+      </c>
+      <c r="E22" s="6">
+        <v>77.3</v>
+      </c>
+      <c r="F22" s="6">
+        <v>206</v>
+      </c>
+      <c r="G22" s="6">
+        <v>32</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>0.2802</v>
+        <v>0.35139999999999999</v>
       </c>
       <c r="D23" s="6">
-        <v>0.27279999999999999</v>
+        <v>0.3306</v>
       </c>
       <c r="E23" s="6">
-        <v>77.5</v>
+        <v>76.900000000000006</v>
       </c>
       <c r="F23" s="6">
-        <v>1467.4</v>
+        <v>58.4</v>
       </c>
       <c r="G23" s="6">
         <v>32</v>
@@ -1135,33 +1134,33 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>0.97489999999999999</v>
-      </c>
-      <c r="D24" s="5">
-        <v>0.94479999999999997</v>
-      </c>
-      <c r="E24" s="5">
-        <v>195.5</v>
-      </c>
-      <c r="F24" s="5">
-        <v>8.9</v>
-      </c>
-      <c r="G24" s="5">
-        <v>224</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.2802</v>
+      </c>
+      <c r="D24" s="6">
+        <v>0.27279999999999999</v>
+      </c>
+      <c r="E24" s="6">
+        <v>77.5</v>
+      </c>
+      <c r="F24" s="6">
+        <v>1467.4</v>
+      </c>
+      <c r="G24" s="6">
+        <v>32</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>13</v>
       </c>
@@ -1189,12 +1188,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H25" xr:uid="{4E1E373F-8B5E-4AA1-B1CE-A13674CA8A61}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="224"/>
-      </filters>
-    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H25">
+      <sortCondition descending="1" ref="G1:G25"/>
+    </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>